--- a/data/trans_camb/P20-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P20-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,29</t>
+          <t>1,19; 6,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,15</t>
+          <t>-1,42; 3,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,09</t>
+          <t>1,35; 7,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,54</t>
+          <t>0,47; 4,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,32</t>
+          <t>-1,78; 2,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,88</t>
+          <t>-2,34; 1,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,4</t>
+          <t>1,42; 4,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,24</t>
+          <t>-1,01; 2,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,06; 3,31</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 110,94</t>
+          <t>13,54; 108,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 55,28</t>
+          <t>-20,23; 64,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,79; 125,33</t>
+          <t>19,23; 129,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 67,75</t>
+          <t>5,68; 72,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 50,28</t>
+          <t>-20,31; 42,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 27,59</t>
+          <t>-26,41; 27,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 68,1</t>
+          <t>16,53; 75,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 33,89</t>
+          <t>-12,66; 35,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 47,77</t>
+          <t>0,55; 51,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,46</t>
+          <t>0,94; 3,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,44</t>
+          <t>0,15; 2,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,8</t>
+          <t>-0,03; 2,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,9</t>
+          <t>0,03; 3,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,9</t>
+          <t>-1,79; 1,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; -0,3</t>
+          <t>-3,78; -0,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,18</t>
+          <t>0,96; 3,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,78</t>
+          <t>-0,43; 1,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,92</t>
+          <t>-1,4; 0,95</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,15; 164,73</t>
+          <t>26,44; 167,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 116,21</t>
+          <t>4,69; 120,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 126,74</t>
+          <t>1,38; 134,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 62,66</t>
+          <t>-0,05; 61,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 30,58</t>
+          <t>-21,61; 26,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,4; -5,74</t>
+          <t>-47,25; -2,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 75,32</t>
+          <t>17,24; 72,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 44,15</t>
+          <t>-8,46; 39,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 20,45</t>
+          <t>-25,78; 21,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,21</t>
+          <t>-3,85; 1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,73</t>
+          <t>-2,25; 3,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,23</t>
+          <t>-0,81; 4,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,91</t>
+          <t>-1,27; 5,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,93</t>
+          <t>-1,88; 4,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,07</t>
+          <t>-3,81; 2,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,46</t>
+          <t>-1,57; 2,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,28</t>
+          <t>-1,3; 3,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,48</t>
+          <t>-1,2; 2,69</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,07; 49,6</t>
+          <t>-73,09; 36,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 123,68</t>
+          <t>-44,33; 102,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 147,35</t>
+          <t>-18,55; 152,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 107,99</t>
+          <t>-15,58; 104,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 89,18</t>
+          <t>-21,16; 81,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 37,28</t>
+          <t>-41,59; 42,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 52,63</t>
+          <t>-24,96; 65,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 68,71</t>
+          <t>-18,52; 68,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 50,92</t>
+          <t>-18,24; 59,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,05</t>
+          <t>0,82; 3,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,69</t>
+          <t>-0,3; 1,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,43</t>
+          <t>-0,09; 2,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,42</t>
+          <t>0,85; 3,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,64</t>
+          <t>-0,79; 1,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,06</t>
+          <t>-2,91; -0,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,01</t>
+          <t>1,26; 3,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,42</t>
+          <t>-0,24; 1,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,85</t>
+          <t>-1,04; 0,82</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,11; 83,21</t>
+          <t>18,76; 87,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 46,48</t>
+          <t>-6,98; 49,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 65,46</t>
+          <t>-1,53; 67,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,79; 51,22</t>
+          <t>10,28; 52,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 24,32</t>
+          <t>-10,28; 25,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,36; -0,85</t>
+          <t>-36,87; -4,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,33; 56,3</t>
+          <t>20,65; 57,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 26,33</t>
+          <t>-4,13; 26,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 15,91</t>
+          <t>-17,15; 15,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P20-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,32</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,09</t>
+          <t>1,15; 6,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,47</t>
+          <t>-1,55; 3,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,04</t>
+          <t>1,13; 6,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,69</t>
+          <t>0,29; 4,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,96</t>
+          <t>-1,84; 3,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,84</t>
+          <t>-2,05; 1,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,81</t>
+          <t>1,35; 4,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,42</t>
+          <t>-0,95; 2,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,31</t>
+          <t>-0,34; 2,97</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,74%</t>
+          <t>-3,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 108,41</t>
+          <t>14,74; 107,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 64,89</t>
+          <t>-21,72; 54,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,23; 129,14</t>
+          <t>14,63; 107,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 72,41</t>
+          <t>3,41; 71,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 42,3</t>
+          <t>-21,66; 49,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 27,56</t>
+          <t>-24,27; 30,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,53; 75,07</t>
+          <t>17,01; 74,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 35,84</t>
+          <t>-12,07; 37,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 51,08</t>
+          <t>-4,52; 45,07</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,39</t>
+          <t>0,83; 3,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,45</t>
+          <t>0,1; 2,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,81</t>
+          <t>0,86; 3,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,8</t>
+          <t>-0,04; 3,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,69</t>
+          <t>-1,63; 1,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -0,17</t>
+          <t>-2,73; 0,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,16</t>
+          <t>0,87; 3,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,72</t>
+          <t>-0,43; 1,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,95</t>
+          <t>-0,45; 1,63</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-27,55%</t>
+          <t>-13,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-3,78%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,44; 167,39</t>
+          <t>26,17; 166,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 120,29</t>
+          <t>2,09; 116,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 134,49</t>
+          <t>25,46; 160,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 61,62</t>
+          <t>-1,48; 62,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 26,79</t>
+          <t>-20,27; 29,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,25; -2,82</t>
+          <t>-32,08; 10,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 72,63</t>
+          <t>15,93; 70,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 39,18</t>
+          <t>-7,94; 40,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 21,63</t>
+          <t>-8,29; 37,68</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,04</t>
+          <t>-3,68; 1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,16</t>
+          <t>-2,25; 3,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,49</t>
+          <t>-1,02; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,96</t>
+          <t>-1,35; 5,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 4,58</t>
+          <t>-1,86; 4,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,34</t>
+          <t>-3,54; 2,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,94</t>
+          <t>-1,71; 2,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,05</t>
+          <t>-1,21; 3,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,69</t>
+          <t>-1,43; 2,52</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-8,36%</t>
+          <t>-7,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,09; 36,98</t>
+          <t>-70,11; 40,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 102,46</t>
+          <t>-41,86; 117,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 152,45</t>
+          <t>-21,58; 143,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 104,05</t>
+          <t>-16,2; 105,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 81,92</t>
+          <t>-20,04; 86,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 42,98</t>
+          <t>-37,49; 41,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 65,68</t>
+          <t>-26,43; 54,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 68,4</t>
+          <t>-17,35; 69,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 59,6</t>
+          <t>-22,48; 56,48</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,09</t>
+          <t>0,82; 3,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,84</t>
+          <t>-0,25; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,49</t>
+          <t>0,69; 2,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,52</t>
+          <t>0,82; 3,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,69</t>
+          <t>-0,93; 1,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,29</t>
+          <t>-2,05; 0,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,01</t>
+          <t>1,1; 2,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,4</t>
+          <t>-0,35; 1,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,82</t>
+          <t>-0,45; 1,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-19,58%</t>
+          <t>-10,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,62%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,76; 87,76</t>
+          <t>16,97; 83,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 49,42</t>
+          <t>-5,65; 50,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 67,12</t>
+          <t>14,1; 77,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,28; 52,18</t>
+          <t>10,57; 52,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 25,04</t>
+          <t>-11,94; 24,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,87; -4,22</t>
+          <t>-25,12; 5,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,65; 57,31</t>
+          <t>17,88; 53,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 26,79</t>
+          <t>-5,91; 25,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 15,29</t>
+          <t>-7,28; 23,08</t>
         </is>
       </c>
     </row>
